--- a/docs/CTRBLXAI_Weapons_Equipment.xlsx
+++ b/docs/CTRBLXAI_Weapons_Equipment.xlsx
@@ -27,10 +27,12 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="004472C4"/>
+      <color rgb="002F5496"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -428,14 +430,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -861,7 +863,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Revised Weapon Archetypes (20 items: 18 weapons + 2 off-hands)</t>
+          <t>Revised Archetypes: 18 weapons + 2 off-hands. All target ~1000 BP.</t>
         </is>
       </c>
     </row>
@@ -871,7 +873,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Focus family dissolved. Channeled projectile (Direct + Ignore LoS, costs BP). All 2H have passive identity.</t>
+          <t>Projectile Types</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Direct = 0 BP. Arc = 30 BP (partial LoS advantage). Channeled = 80 BP (full LoS ignore, min range still applies).</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Locked</t>
         </is>
       </c>
     </row>
@@ -886,17 +898,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Family / Projectile</t>
+          <t>Dmg / WT / Dly / Def</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hands</t>
+          <t>Hands | MinR-MaxR | Pattern | Proj | Passive (BP)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Passive / Identity</t>
+          <t>L99 BP</t>
         </is>
       </c>
     </row>
@@ -924,17 +936,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>65 / 165 / 28 / 10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 1 | Cleave | None | — (Cleave=598 pattern)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pattern: Cleave. Multi-target melee.</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -949,17 +961,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>45 / 25 / 110 / -5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 1 | Single | None | Stagger (100)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Passive: Stagger (fixed BP → bonus RT Delay). Fast, low WT.</t>
+          <t>988</t>
         </is>
       </c>
     </row>
@@ -974,17 +986,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>97 / 107 / 20 / -20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 1 | Single | None | Brutal (100)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Passive: Brutal (fixed BP → bonus Damage). Glass cannon.</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -999,17 +1011,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>42 / 90 / 45 / 21</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 1-2 | Line 2 | None | Fortify (120)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pattern: Line 2, Range 2. Passive: Fortify (Def% per unit hit until next turn).</t>
+          <t>1011</t>
         </is>
       </c>
     </row>
@@ -1024,17 +1036,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>80 / 130 / 110 / 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 1 | Single | None | Knockback (150)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Passive: Knockback (collision/fall damage). High Damage, high WT.</t>
+          <t>1004</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1074,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>67 / 60 / 60 / 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1H | 1 | Single | None | — (reference)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No passive. Balanced reference.</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -1087,17 +1099,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>60 / 10 / 20 / 6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1H | 1 | Single | None | Piercing Edge (120)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Passive: Piercing Edge (pending). Best Damage/CT.</t>
+          <t>996</t>
         </is>
       </c>
     </row>
@@ -1112,17 +1124,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>52 / 80 / 45 / 0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1H | 1-3 | Single | None | — (Range 3 melee)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>No passive. Range 3 melee, no LoS restriction, no dead zone.</t>
+          <t>998</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1149,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>37 / 70 / 64 / 19</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1H | 1 | Single | None | Knockback (150)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Passive: Knockback 1. Burst RT Delay + displacement.</t>
+          <t>997</t>
         </is>
       </c>
     </row>
@@ -1162,17 +1174,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Melee / None</t>
+          <t>41 / 25 / 53 / 44</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1H | 1 | Single | None | — (Def identity)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>No passive. Highest Defense among 1H.</t>
+          <t>993</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1212,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ranged / Direct</t>
+          <t>34 / 20 / 64 / 0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 2-4 | Single | Direct | Armor Pierce (130)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Passive: Armor Pierce (ignores % Def). Low WT. Anti-tank.</t>
+          <t>995</t>
         </is>
       </c>
     </row>
@@ -1225,17 +1237,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ranged / Channeled</t>
+          <t>58 / 60 / 40 / 0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 2-4 | Single | Channeled(80) | Arcane Reach (120)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Channeled (Ignore LoS, costs BP, min range applies). Passive: Extend Skill Range. Range 4.</t>
+          <t>1003</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1262,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ranged / Arc</t>
+          <t>63 / 115 / 71 / -5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 2-4 | Single | Arc(30) | High Ground (100)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Passive: Range (fixed BP, lower). Mid-range, balanced, good RT Delay.</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -1275,17 +1287,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ranged / Arc</t>
+          <t>50 / 130 / 20 / -5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 2-5 | Single | Arc(30) | Range +1 (190)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Passive: Range (fixed BP, higher). Greatest range, high min range, high WT.</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -1300,17 +1312,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ranged / Arc</t>
+          <t>43 / 215 / 20 / -5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2H</t>
+          <t>2H | 3-5 | Impact Splash | Arc(30) | — (Splash=400 pattern)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pattern: Impact Splash. AOE from distance, high min range, high WT.</t>
+          <t>1002</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1350,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ranged / Direct</t>
+          <t>20 / 70 / 58 / 0</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1H | 2-4 | Single | Direct | — (RT Delay identity)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>No passive. Range 4, low damage, high RT Delay.</t>
+          <t>991</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1375,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ranged / Channeled</t>
+          <t>25 / 50 / 45 / 0</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1H | 2-3 | Single | Channeled(80) | Arcane Flow (80)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Channeled (Ignore LoS, costs BP, min range applies). Passive: MP Recovery.</t>
+          <t>990</t>
         </is>
       </c>
     </row>
@@ -1388,17 +1400,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ranged / Direct</t>
+          <t>15 / 60 / 0 / 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1H | 2-4 | Single | Direct | Venomous (200)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Passive: Poison. Range 4, very low damage.</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1420,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>--- Off-hand Equipment ---</t>
+          <t>--- Off-hand Equipment (350 BP total budget each) ---</t>
         </is>
       </c>
       <c r="C47" s="2" t="n"/>
@@ -1431,12 +1443,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1H (off)</t>
+          <t>1H (off) | Improves Guard effectiveness + Defense stats</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Improves Guard effectiveness + Defense stats.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1468,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1H (off)</t>
+          <t>1H (off) | Improves Skill Potency. Not a weapon.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Improves Skill Potency. Not a weapon.</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -2504,6 +2516,1340 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>350</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>--- PASSIVE DEFINITIONS ---</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Brutal</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>War Axe</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>On hit. Effective Weapon Damage = Base Weapon Damage × 1.20. Attack Power then uses Effective Weapon Damage × (1 + STR / 200). Adds to base BEFORE STR scaling. Only valuable on high-base-damage weapons.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>100 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Stagger</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Claws</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>On hit. Effective RT Delay = Base Weapon RT Delay × 1.25. Applied before throughput calculation. Only valuable on high-base-delay + low-WT weapons.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>100 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Knockback</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hammer, Club</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>On hit. Push target floor(Force / 2) tiles directly away. Force = 1 + floor(STR / 60). Collision: if blocked tile, target takes floor(Final Damage × 0.30) collision damage. Fall: normal fall damage rules apply if pushed off elevation.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>150 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Fortify</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Spear</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>On hit (once per unit hit). Gain Fortify buff: +20% of base Weapon Defense as flat Defense bonus per unit hit. Duration: until end of this unit next turn. Multiple hits stack (Line 2 = 2 units = +40%). Replaces previous Fortify — does not stack across turns.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>120 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Armor Pierce</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Crossbow</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>On hit. Reduce effective target Defense by 30% before damage resolution. Applied Defense = Target Defense × 0.70. Applies to Basic Attack and Skills that inherit weapon damage. Does not apply to skills with authored independent Power Formulas.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>130 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>High Ground</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Great Bow</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Passive (always active). When attacking from higher elevation than target, increase the elevation damage bonus by 35%. Only triggers when attacker has elevation advantage.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>100 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Range +1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Longbow (and eligible procedural rarity rolls)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Passive (always active). +1 to Maximum Range. Effective Max Range = base Max Range + 1. Minimum Range unchanged. Non-exclusive — can appear in procedural bonus attribute rolls on eligible weapons. Only cost-efficient at base Range 5+ (curve marginal at R5→6 = 204 BP &gt; passive 190 BP).</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>190 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Arcane Reach</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Passive (always active). Skills that explicitly inherit weapon range gain +1 bonus Maximum Range on top of inherited value. Does not apply to skills with authored independent ranges. Does not extend Minimum Range.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>120 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Arcane Flow</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Wand</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>On ready turn. Recover MP = 5 + floor(INT / 20). Does not trigger during channeling, stun, or sleep. At INT=0: +5 MP/turn. At INT=60: +8 MP/turn.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>80 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Venomous</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Blowgun</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>On hit. Apply Poison status. Poison damage per turn = floor(Target Max HP × 0.04). Duration: 3 turns. Reapplication refreshes duration. Poison ignores Defense and does not scale with attacker stats.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>200 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Piercing Edge</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Dagger</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PENDING DEFINITION. Provisional 120 BP allocation. Effect intended to support Dagger best Damage/CT identity. Do not use Dagger as final passive-balanced reference until defined.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>120 BP (provisional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>--- PROJECTILE TYPE COSTS ---</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>All direct projectile weapons</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Requires full Line of Sight. Blocked by terrain, walls, elevation, and allied units.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Arc</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Great Bow, Longbow, Bazooka</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Partial LoS advantage — arcs over low obstacles and allies. Still requires valid path. Min-range refund eligible.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>30 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Channeled</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Staff, Wand</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Full LoS ignore — terrain, walls, elevation, allied units do not block. Min range still applies. Direct trajectory. BP cost reflects full terrain bypass advantage.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>80 BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>--- NEW 1H WEAPONS (10) ---</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Rapier</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>66 / 33 / 25 / 0</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1H | 1 | Single | None | Precision Strike (130): +15% Hit Quality on Basic Attacks</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sickle</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>59 / 64 / 53 / 0</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1H | 1 | Single | None | Drain (120): heal 5% of final damage dealt per hit</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Torch</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>38 / 35 / 54 / 9</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1H | 1 | Single | None | Ignite (150): applies Burn DoT on hit</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Fan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>57 / 75 / 15 / -5</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1H | 1 | Adjacent(300) | None | — (pattern is identity)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Flail</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>59 / 61 / 49 / -3</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1H | 1 | Single | None | Bypass (140): ignores target Guard mitigation</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Hatchet</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>64 / 35 / 28 / 4</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1H | 1 | Single | None | Executioner (110): +40% damage vs targets below 30% HP</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Needle</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>29 / 64 / 54 / -3</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1H | 2-3 | Single | Direct | True Strike (150): attacks resolve at maximum Hit Quality</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Boomerang</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>39 / 74 / 42 / -3</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1H | 2-3 | Single | Arc(30) | Return (130): passive/status triggers on throw AND return</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Throwing Knife</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>47 / 40 / 25 / -3</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1H | 2-3 | Single | Direct | Backstab (120): +50% damage when attacking from behind</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Bell</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>12 / 45 / 32 / 2</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1H | 2-3 | Single | Channeled(80) | Lullaby (180): applies Sleep on hit</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>--- NEW 2H WEAPONS (10) ---</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Scythe</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>64 / 177 / 15 / -5</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2H | 1 | Cleave(598) | None | Reap (100): heal 5% of total Cleave damage dealt</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Lance</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>91 / 100 / 29 / 2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2H | 1 | Single | None | Charge (130): +50% damage if unit Moved this turn</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Flameberge</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>87 / 100 / 59 / 5</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2H | 1 | Single | None | Lacerate (140): applies Bleed on hit</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Greatshield</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>59 / 60 / 79 / 54</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2H | 1 | Single | None | Bulwark (150): add 25% of base Weapon Defense to base Weapon Damage before STR scaling</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Chains</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>50 / 50 / 89 / 24</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2H | 1-2 | Single | None | Pull (150): drag target floor(Force/2) tiles toward attacker</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Mortar</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>59 / 161 / 15 / -8</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2H | 4-5 | Impact Splash(400) | Arc(30) | — (highest min range AOE, committed artillery)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ballista</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>58 / 153 / 15 / -8</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2H | 2-4 | Line 2(400) | Direct | — (ranged piercing line)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Javelin</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>64 / 93 / 54 / -5</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2H | 2-3 | Adjacent(300) | Arc(30) | — (mid-range splash on impact)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Frost Rod</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>34 / 50 / 54 / 1</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2H | 2-4 | Single | Channeled(80) | Freeze (180): applies Freeze on hit</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>War Horn</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>5 / 68 / 94 / 0</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2H | 1-2 | Impact Splash(400) | Channeled(80) | — (zero damage, pure AOE RT Delay)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>--- NEW OFF-HAND EQUIPMENT (15 new + 2 existing revised) ---</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>All off-hands: base WT=20. Linear pricing: Dmg=5 BP/pt, Def=4 BP/pt, WT reduction=3 BP/pt, RT Delay=3 BP/pt. Total budget=350 BP.</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Stat-bonus passives (e.g. Brutal) use owning item base stat only, not main weapon.</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Shield (revised)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Dmg=0 / WT=20 / Dly=0 / Def=57</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Passive: Guard Bonus +15% mitigation (120 BP). Stat BP=228. Total=348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Orb (revised)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Dmg=50 / WT=20 / Dly=0 / Def=0</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Passive: Skill Potency +8% (100 BP). Stat BP=250. Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Buckler</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Dmg=0 / WT=20 / Dly=10 / Def=55</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Passive: Deflect — on Guard, reflect 20% of mitigated damage (130 BP). Stat BP=220. Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Tome</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Dmg=23 / WT=20 / Dly=0 / Def=28</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Passive: Lore — +30% applied status/buff duration (120 BP). Stat BP=227. Total=347.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Lantern</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Dmg=18 / WT=20 / Dly=0 / Def=45</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Passive: Illumination — +2 Discovery Radius, reveal traps (80 BP). Stat BP=270. Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Quiver</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Dmg=40 / WT=20 / Dly=0 / Def=0</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Passive: Quick Draw — if prior 2 actions were Basic Attacks, allow 1 bonus BA this turn (150 BP). Stat BP=200. Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Totem</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Dmg=17 / WT=20 / Dly=0 / Def=41</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Passive: Spirit Link — +40% Summon HP and duration (100 BP). Stat BP=249. Total=349.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Parrying Dagger</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dmg=33 / WT=20 / Dly=0 / Def=21</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Passive: +15% final Evasiveness (100 BP). Stat BP=249. Total=349.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Dmg=46 / WT=20 / Dly=0 / Def=0</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Passive: Attunement — +25% elemental damage dealt (120 BP). Stat BP=230. Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Dmg=15 / WT=20 / Dly=0 / Def=36</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Passive: Rally — aura, adjacent allies +10% damage dealt (130 BP). Stat BP=219. Total=349.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Talisman</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Dmg=17 / WT=20 / Dly=0 / Def=41</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Passive: Ward — reduce incoming debuff duration by 40% (100 BP). Stat BP=249. Total=349.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Prism</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Dmg=50 / WT=20 / Dly=0 / Def=0</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Passive: Precision — +15% Hit Quality bonus (100 BP). Stat BP=250. Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Kite</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Dmg=0 / WT=20 / Dly=3 / Def=62</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Passive: Brace — reduce incoming RT Delay by 30% (100 BP). Stat BP=248+9=257. Total=348.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Skull</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Dmg=54 / WT=20 / Dly=0 / Def=0</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Passive: Fortune — +20% Fortune Multiplier bonus (80 BP). Stat BP=270. Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Dmg=46 / WT=20 / Dly=0 / Def=0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Passive: Entangle — on hit, reduce target Evasiveness by 40% for 1 turn (120 BP). Stat BP=230. Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dmg=0 / WT=20 / Dly=25 / Def=36</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Passive: Patience — if no attack/skill last turn, next attack/skill deals +30% damage (130 BP). Stat BP=219. Total=349.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Wind Vane</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Dmg=28 / WT=0 / Dly=0 / Def=0</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Passive: Lightweight — reduce total equipped WT (weapon+off-hand) by 0.3 per unit level, min 0 (150 BP). Stat BP=200 (Dmg=140+WTred=60). Total=350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>--- NEW STATUS: SLEEP ---</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Duration: 3 turns. Unit automatically takes Rest/Wait each turn. Damage from any source removes Sleep immediately. While sleeping: recover HP and MP by 3% per 200 CT.</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Classification: Hard control with benefit trade-off (enemy heals while CC'd). Applied by: Bell (Lullaby passive).</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>--- OFF-HAND BP MODEL ---</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Off-hand budget = 350 BP. Base WT = 20 (standardized). Linear stat pricing: Damage = 5 BP/pt, Defense = 4 BP/pt, WT reduction (below 20) = 3 BP/pt, RT Delay = 3 BP/pt.</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Stat-bonus passives (Brutal, Stagger, etc.) always use the OWNING ITEM base stat for calculation, never main weapon or combined total. Same passive = same BP cost regardless of item slot.</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>--- PATTERN ADDITIONS ---</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Adjacent = 300 BP (hits units on both sides of target, ~0.75 secondary target equivalents × reliability). Used by: Fan (1H), Javelin (2H).</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>All existing patterns preserved: Single=0, Line 2=400, Cleave=598, Impact Splash=400.</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Locked</t>
         </is>
       </c>
     </row>
